--- a/data_extactor/batch_10_fa/batch_0074_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0074_fa.xlsx
@@ -513,22 +513,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | خدمات مشتریان و شخصی | مکانیک | مدیریت و سرپرستی | آموزش و تربیت | ریاضیات | ایمنی و امنیت عمومی | تولید و فرآوری | زبان انگلیسی | طراحی | فروش و بازاریابی | پرسنل و منابع انسانی | حمل‌ونقل</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | آموزش و پرورش | ریاضیات | ایمنی و امنیت عمومی | تولید و فرآوری | زبان انگلیسی | طراحی | فروش و بازاریابی | پرسنل و منابع انسانی | حمل و نقل</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | انعطاف‌پذیری حرکتی | حساسیت به مشکلات | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | بینایی نزدیک | تعادل عمومی بدن | قدرت ایستا | هماهنگی چندعضوی | زبردستی دستی | ثبات دست و بازو | توجه انتخابی | هماهنگی عمومی بدن | زبردستی انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
+          <t>قدرت تنه | انعطاف‌پذیری دامنه حرکت | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | بینایی نزدیک | تعادل کلی بدن | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | توجه انتخابی | هماهنگی کلی بدن | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای بالا رفتن از نردبان، داربست یا تیرها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | داخل ساختمان، بدون کنترل شرایط محیطی | سلامت و ایمنی سایر کارگران | ارتباط با دیگران | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | قرار گرفتن در معرض ارتفاعات بالا | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، کمربند ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | محیط داخلی، بدون کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | قرار گرفتن در معرض ارتفاعات بالا | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | بناهای آجری و بلوکی | نصابان فرش | نصابان دیوار خشک و تایل سقف | لمینت‌کاران و سازندگان فایبرگلاس | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | دستیاران--لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران عایق‌کاری، کف، سقف و دیوار | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | لوله‌گذاران | گچ‌کاران و بناهای سیمان‌کاری | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | سقف‌سازان | کارگران ورق‌کاری | نصابان و تکنسین‌های حرارتی خورشیدی | کارگران آهن و فولاد سازه‌ای | سازندگان و مونتاژکنندگان فلزات سازه‌ای | نوارکش‌ها | کاشی‌کاران و سنگ‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برنج‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | بنّایان آجرکار و بلوک‌کار | نصّابان موکت و فرش | نصابان دیوار خشک و تایل سقف | لمینت‌کاران و سازندگان فایبرگلاس | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری کف، سقف و دیوار | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | لوله‌گذاران | گچ‌کاران و بناهای سیمان‌کاری | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | سقف‌سازان | کارگران ورق‌کاری | نصابان و تکنسین‌های حرارتی خورشیدی | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | تپرز | کاشی‌کاران و سنگ‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ساختمان و ساخت‌وساز</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | بینایی نزدیک | زبردستی دستی | قدرت بالاتنه | وضوح گفتار | تشخیص رنگ بصری | تعادل عمومی بدن | هماهنگی عمومی بدن | انعطاف‌پذیری حرکتی | هماهنگی چندعضوی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | مهارت دستی | قدرت تنه | وضوح گفتار | تشخیص رنگ بصری | تعادل کلی بدن | هماهنگی کلی بدن | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای بالا رفتن از نردبان، داربست یا تیرها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارگران | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارگران | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
+          <t>صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بناهای آجری و بلوکی | نجاران | بناهای سیمان و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | پرداخت‌کاران مبلمان | دستیاران--بناهای آجری، بلوکی، سنگ‌کاران و کاشی‌کاران و مرمرکاران | دستیاران--نجاران | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای سیمان‌کاری | دستیاران--سقف‌سازان | کارگران عایق‌کاری، کف, سقف و دیوار | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزئینات | کاغذدیواری‌کن‌ها | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | کارگران و پرداخت‌کاران موزاییک درجا | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | پرداخت‌کاران مبلمان | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--سقف‌سازان | کارگران عایق‌کاری کف، سقف و دیوار | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | کاغذدیواری‌کن‌ها | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخنرانی | گوش دادن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ساختمان و ساخت‌وساز | ریاضیات | مکانیک | ایمنی و امنیت عمومی | مدیریت و سرپرستی</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | ریاضیات | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | زبردستی دستی | ثبات دست و بازو | انعطاف‌پذیری حرکتی | هماهنگی چندعضوی | تعادل عمومی بدن | زبردستی انگشتان | قدرت بالاتنه | دقت کنترل | ترتیب‌دهی اطلاعات | درک شفاهی</t>
+          <t>بینایی نزدیک | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | تعادل کلی بدن | مهارت انگشتان | قدرت تنه | دقت کنترل | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | صرف زمان برای بالا رفتن از نردبان، داربست یا تیرها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای خم کردن یا چرخاندن بدن</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نجاران | نصابان فرش | نصابان دیوار خشک و تایل سقف | لمینت‌کاران و سازندگان فایبرگلاس | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | سنباده‌زنان و پرداخت‌کاران کف | پرداخت‌کاران مبلمان | شیشه‌بران | دستیاران--بناهای آجری، بلوکی، سنگ‌کاران و کاشی‌کاران و مرمرکاران | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای سیمان‌کاری | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران شابلون‌زنی، فلز و پلاستیک | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزئینات | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | کارگران ورق‌کاری | کارگران و پرداخت‌کاران موزاییک درجا | کاشی‌کاران و سنگ‌کاران</t>
+          <t>نجّاران | نصّابان موکت و فرش | نصابان دیوار خشک و تایل سقف | لمینت‌کاران و سازندگان فایبرگلاس | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | سنباده‌کاران و پرداخت‌کاران کف | پرداخت‌کاران مبلمان | شیشه‌بران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران شابلون‌زنی، فلز و پلاستیک | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | کارگران ورق‌کاری | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخنرانی | گوش دادن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دقت کنترل | ثبات دست و بازو | درک شفاهی | قدرت ایستا | وضوح گفتار | تشخیص گفتار | درک عمق | بینایی نزدیک | حساسیت به مشکلات | بیان شفاهی | انعطاف‌پذیری حرکتی | استقامت | قدرت بالاتنه | زمان عکس‌العمل | کنترل نرخ | هماهنگی چندعضوی | زبردستی انگشتان | زبردستی دستی | توجه انتخابی | تجسم فضایی | ترتیب‌دهی اطلاعات</t>
+          <t>دقت کنترل | ثبات دست و بازو | درک شفاهی | قدرت ایستا | وضوح گفتار | تشخیص گفتار | درک عمق | بینایی نزدیک | حساسیت به مسئله | بیان شفاهی | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، قرار گرفتن در معرض تمام شرایط جوی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | نزدیکی فیزیکی | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | دیگ‌سازان | بناهای آجری و بلوکی | نجاران | بناهای سیمان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | نصابان دیوار خشک و تایل سقف | نصابان و تعمیرکاران خطوط انتقال نیروی برق | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، استخراج سطحی | دستیاران--لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | اپراتورهای تجهیزات روسازی، آسفالت و کوبش | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران آهن تقویتی و میلگرد | اپراتورهای دکل حفاری چرخشی، نفت و گاز | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | کارگران ورق‌کاری | کارگران آهن و فولاد سازه‌ای</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | نصابان دیوار خشک و تایل سقف | نصابان و تعمیرکاران خطوط انتقال نیروی برق | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران آهن تقویتی و میلگرد | اپراتورهای مته چرخشی، نفت و گاز | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AEC Design Group CADPIPE | Atlas Construction Business Forms | Autodesk Building Systems | Bentley Systems AutoPIPE | Bookkeeping software | COADE CAESAR II | Database software | Drawing and drafting software | Elite Software DPIPE | Elite Software FIRE | Elite Software HSYM | Elite Software Plumbing CAD | Elite Software Spipe | Elite Software Sprinkler CAD | Email software | Estimating software | FastEST FastPipe | FastEST software | Heat loss calculation software | Horizon Engineering Sigma Plumbing Calculator | Insight Direct ServiceCEO | Intuit QuickBooks | Job costing software | KRS Enterprises Service First! | Klear Estimator | Maintenance management software | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Pipepro Pipefitting | Piping construction costs estimation software | PipingOffice | PricePoint | Quicken | Quote Software QuoteExpress | Vision InfoSoft Plumbing Bid Manager | ViziFlow | Watter Hammer Software Hytran | Wilhelm Publishing Threshold | Wintac Pro</t>
+          <t>AEC Design Group CADPIPE | Atlas Construction Business Forms | Autodesk Building Systems | Bentley Systems AutoPIPE | نرم‌افزار حسابداری | COADE CAESAR II | نرم‌افزار پایگاه داده | نرم‌افزار ترسیم و طراحی | Elite Software DPIPE | Elite Software FIRE | Elite Software HSYM | Elite Software Plumbing CAD | Elite Software Spipe | Elite Software Sprinkler CAD | نرم‌افزار ایمیل | Estimating software | FastEST FastPipe | FastEST software | Heat loss calculation software | Horizon Engineering Sigma Plumbing Calculator | Insight Direct ServiceCEO | Intuit QuickBooks | نرم‌افزار هزینه‌یابی کار | KRS Enterprises Service First! | Klear Estimator | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Pipepro Pipefitting | Piping construction costs estimation software | PipingOffice | PricePoint | Quicken | Quote Software QuoteExpress | Vision InfoSoft Plumbing Bid Manager | ViziFlow | Watter Hammer Software Hytran | Wilhelm Publishing Threshold | Wintac Pro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخنرانی</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مکانیک | طراحی | ریاضیات | خدمات مشتریان و شخصی | مدیریت و سرپرستی | مهندسی و فناوری | ایمنی و امنیت عمومی | فیزیک</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | طراحی | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره | مهندسی و فناوری | ایمنی و امنیت عمومی | فیزیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | زبردستی انگشتان | بینایی نزدیک | زبردستی دستی | استدلال قیاسی | استدلال استقرایی | بینایی دور | قدرت بالاتنه | انعطاف‌پذیری دسته‌بندی | تجسم فضایی | ثبات دست و بازو | درک شفاهی | بیان شفاهی | هماهنگی چندعضوی | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری حرکتی | قدرت پویا | قدرت ایستا | سرعت ادراکی | انعطاف‌پذیری بستار | درک کتبی</t>
+          <t>حساسیت به مسئله | مهارت انگشتان | بینایی نزدیک | مهارت دستی | استدلال قیاسی | استدلال استقرایی | بینایی دور | قدرت تنه | انعطاف‌پذیری دسته‌بندی | تجسم | ثبات دست و بازو | درک شفاهی | بیان شفاهی | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دامنه حرکت | قدرت پویا | قدرت ایستا | سرعت ادراکی | انعطاف‌پذیری بستار | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فشار زمانی | داخل ساختمان، بدون کنترل شرایط محیطی | سلامت و ایمنی سایر کارگران | اهمیت دقیق یا درست بودن | ارتباط با دیگران | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، قرار گرفتن در معرض تمام شرایط جوی | صرف زمان برای راه رفتن یا دویدن | نزدیکی فیزیکی | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض ارتفاعات بالا | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای بالا رفتن از نردبان، داربست یا تیرها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | سطح رقابت | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، کمربند ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | ارتباط با دیگران | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای راه رفتن یا دویدن | نزدیکی فیزیکی | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض ارتفاعات بالا | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | دیگ‌سازان | نجاران | کارگران ساختمانی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | برقی‌کاران | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--برقی‌کاران | دستیاران--کارگران نصب، تعمیر و نگهداری | دستیاران--لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران تعمیر و نگهداری، عمومی | آسیابان‌ها | لوله‌گذاران | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | کارگران ورق‌کاری | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان تاسیسات و اپراتورهای دیگ بخار | کارگران آهن و فولاد سازه‌ای</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نجّاران | کارگران ساختمانی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | برق‌کاران | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری کف، سقف و دیوار | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | لوله‌گذاران | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | کارگران ورق‌کاری | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان تاسیسات و اپراتورهای دیگ بخار | کارگران سازه‌های آهنی و فولادی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1CadCam Unigraphics | Adobe Photoshop | Autodesk AutoCAD | Computer-aided drafting or design software | Cost estimating software | Dassault Systemes CATIA | Dassault Systemes SolidWorks | Inventory control system software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic for Applications VBA | Microsoft Word | National Instruments LabVIEW | Oracle Java | PTC Pro/ENGINEER Wildfire | Salesforce software | Work scheduling software</t>
+          <t>1CadCam Unigraphics | Adobe Photoshop | Autodesk AutoCAD | نرم‌افزار نقشه‌کشی یا طراحی به کمک کامپیوتر | نرم‌افزار برآورد هزینه | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار سیستم کنترل موجودی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic for Applications VBA | Microsoft Word | National Instruments LabVIEW | Oracle Java | PTC Pro/ENGINEER Wildfire | نرم‌افزار Salesforce | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخنرانی | گوش دادن فعال | یادگیری فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتریان و شخصی | زبان انگلیسی | مهندسی و فناوری | آموزش و تربیت | طراحی | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | تولید و فرآوری | مدیریت و سرپرستی | ریاضیات</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | طراحی | ایمنی و امنیت عمومی | رایانه و الکترونیک | تولید و فرآوری | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری حرکتی | حساسیت به مشکلات | بیان شفاهی | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | ثبات دست و بازو | تشخیص رنگ بصری | بینایی دور | زبردستی انگشتان | تجسم فضایی | قدرت بالاتنه | زبردستی دستی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی</t>
+          <t>درک شفاهی | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | حساسیت به مسئله | بیان شفاهی | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | ثبات دست و بازو | تشخیص رنگ بصری | بینایی دور | مهارت انگشتان | تجسم | قدرت تنه | مهارت دستی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | فشار زمانی | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | فضای باز، قرار گرفتن در معرض تمام شرایط جوی | کار با یا مشارکت در یک گروه کاری یا تیم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | سلامت و ایمنی سایر کارگران | داخل ساختمان، بدون کنترل شرایط محیطی | قرار گرفتن در معرض ارتفاعات بالا | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامدهای کاری و نتایج سایر کارگران | صرف زمان به صورت ایستاده | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | ایمیل</t>
+          <t>آزادی در تصمیم‌گیری | فشار زمانی | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | فضای باز، در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض ارتفاعات بالا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای ایستادن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ایمیل</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مهندسان برق | مهندسان انرژی، به جز باد و خورشید | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | تکنسین‌های نیروگاه‌های برق‌آبی | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران تعمیر و نگهداری، عمومی | مهندسان مکانیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | اپراتورهای نیروگاه | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان فتوولتائیک خورشیدی | نصابان و تکنسین‌های بهینه‌سازی مصرف انرژی ساختمان | تکنسین‌های خدمات توربین بادی</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مهندسان برق | مهندسان انرژی، به جز باد و خورشید | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | تکنسین‌های نیروگاه برق‌آبی | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران نگهداری و تعمیرات عمومی | مهندسان مکانیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | اپراتورهای نیروگاه برق | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های عایق‌سازی و مقاوم‌سازی در برابر شرایط جوی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A-Systems JobView | Autodesk 3ds Max Design | Autodesk Maya | Construction Software Center EasyEst | Corel Paint Shop Pro | Corel Painter | Cost estimating software | Dassault Systemes CATIA | Embedded systems development software | IBM Maximo Asset Management | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Oracle Database | Sage Construction Anywhere | Salesforce software | Turtle Creek Software Goldenseal</t>
+          <t>A-Systems JobView | Autodesk 3ds Max Design | Autodesk Maya | Construction Software Center EasyEst | Corel Paint Shop Pro | Corel Painter | نرم‌افزار برآورد هزینه | Dassault Systemes CATIA | نرم‌افزار توسعه سیستم‌های تعبیه‌شده | IBM Maximo Asset Management | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Oracle Database | Sage Construction Anywhere | نرم‌افزار Salesforce | Turtle Creek Software Goldenseal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مدیریت و سرپرستی | طراحی | زبان انگلیسی | خدمات مشتریان و شخصی</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | طراحی | زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | زبردستی دستی | انعطاف‌پذیری حرکتی | قدرت بالاتنه | هماهنگی چندعضوی | قدرت ایستا | تعادل عمومی بدن | بیان شفاهی | حساسیت به مشکلات | استقامت | قدرت پویا | تجسم فضایی | وضوح گفتار | تشخیص رنگ بصری | هماهنگی عمومی بدن | دقت کنترل | زبردستی انگشتان | ترتیب‌دهی اطلاعات | درک شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو | قدرت ایستا | تعادل کلی بدن | بیان شفاهی | حساسیت به مسئله | استقامت | قدرت پویا | تجسم | وضوح گفتار | تشخیص رنگ بصری | هماهنگی کلی بدن | دقت کنترل | مهارت انگشتان | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت ایستاده | فضای باز، قرار گرفتن در معرض تمام شرایط جوی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | فضای باز، در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بناهای آجری و بلوکی | نجاران | بناهای سیمان و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | پرداخت‌کاران مبلمان | شیشه‌بران | دستیاران--بناهای آجری، بلوکی، سنگ‌کاران و کاشی‌کاران و مرمرکاران | دستیاران--نجاران | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای سیمان‌کاری | دستیاران--سقف‌سازان | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزئینات | سقف‌سازان | نوارکش‌ها | کارگران و پرداخت‌کاران موزاییک درجا | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | پرداخت‌کاران مبلمان | شیشه‌بران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--سقف‌سازان | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | سقف‌سازان | تپرز | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | ریاضیات | مدیریت و سرپرستی | طراحی | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | مدیریت و اداره | طراحی | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | قدرت ایستا | هماهنگی چندعضوی | زبردستی دستی | انعطاف‌پذیری حرکتی | ثبات دست و بازو | استقامت | بینایی نزدیک | زبردستی انگشتان | دقت کنترل | زمان عکس‌العمل | حساسیت به مشکلات | قدرت پویا | تعادل عمومی بدن | هماهنگی عمومی بدن | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
+          <t>قدرت تنه | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | استقامت | بینایی نزدیک | مهارت انگشتان | دقت کنترل | زمان عکس‌العمل | حساسیت به مسئله | قدرت پویا | تعادل کلی بدن | هماهنگی کلی بدن | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>فضای باز، قرار گرفتن در معرض تمام شرایط جوی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | پیامدهای کاری و نتایج سایر کارگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت ایستاده | صرف زمان برای خم کردن یا چرخاندن بدن | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | سطح رقابت | صرف زمان برای راه رفتن یا دویدن | نزدیکی فیزیکی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض ارتفاعات بالا | تاثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، کمربند ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تشعشع</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | صرف زمان برای خم کردن یا چرخاندن بدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | مکالمات تلفنی | سطح رقابت | صرف زمان برای راه رفتن یا دویدن | نزدیکی فیزیکی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض ارتفاعات بالا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | دیگ‌سازان | بناهای آجری و بلوکی | نجاران | بناهای سیمان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | نصابان حصار | قالب‌ریزان و ماهیچه‌سازان ریخته‌گری | دستیاران--بناهای آجری، بلوکی، سنگ‌کاران و کاشی‌کاران و مرمرکاران | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران شابلون‌زنی، فلز و پلاستیک | آسیابان‌ها | لوله‌گذاران | کارگران ورق‌کاری | کارگران آهن و فولاد سازه‌ای | سازندگان و مونتاژکنندگان فلزات سازه‌ای | کارگران و پرداخت‌کاران موزاییک درجا | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | نصابان حصار | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران شابلون‌زنی، فلز و پلاستیک | مهندسان نصب ماشین‌آلات | لوله‌گذاران | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ASR Software LWC-Plus | ASR Software Taper-Plus | ASR Software TopView LE | ASR Software TopView ME | AppliCad Roof Wizard | CADAFIS | DigiTools Roof CAD | Energy cost evaluation software | Exele TopView | Humidity and vapor drive calculation software | Insight Direct ServiceCEO | Maintenance record software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Roof Pro Estimate Software Roof Pro | RoofLogic | Roofing Calculator | Wintac Pro | Ziatek RoofDraw</t>
+          <t>ASR Software LWC-Plus | ASR Software Taper-Plus | ASR Software TopView LE | ASR Software TopView ME | AppliCad Roof Wizard | CADAFIS | DigiTools Roof CAD | Energy cost evaluation software | Exele TopView | Humidity and vapor drive calculation software | Insight Direct ServiceCEO | نرم‌افزار ثبت تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Roof Pro Estimate Software Roof Pro | RoofLogic | Roofing Calculator | Wintac Pro | Ziatek RoofDraw</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخنرانی</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | خدمات مشتریان و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | آموزش و تربیت | ریاضیات | طراحی | مکانیک | مدیریت و سرپرستی</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | آموزش و پرورش | ریاضیات | طراحی | مکانیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تعادل عمومی بدن | انعطاف‌پذیری حرکتی | قدرت بالاتنه | حساسیت به مشکلات | بینایی نزدیک | هماهنگی چندعضوی | زبردستی دستی | ثبات دست و بازو | درک شفاهی | هماهنگی عمومی بدن | استقامت | قدرت ایستا | دقت کنترل | زبردستی انگشتان | بینایی دور | تشخیص گفتار | توجه انتخابی | تجسم فضایی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
+          <t>تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | حساسیت به مسئله | بینایی نزدیک | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | درک شفاهی | هماهنگی کلی بدن | استقامت | قدرت ایستا | دقت کنترل | مهارت انگشتان | بینایی دور | تشخیص گفتار | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>فضای باز، قرار گرفتن در معرض تمام شرایط جوی | قرار گرفتن در معرض ارتفاعات بالا | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | فراوانی تصمیم‌گیری | صرف زمان به صورت ایستاده | داخل ساختمان، بدون کنترل شرایط محیطی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | هماهنگ کردن یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای راه رفتن یا دویدن</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض ارتفاعات بالا | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بناهای آجری و بلوکی | نجاران | نصابان فرش | بناهای سیمان و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | شیشه‌بران | دستیاران--بناهای آجری، بلوکی، سنگ‌کاران و کاشی‌کاران و مرمرکاران | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای سیمان‌کاری | دستیاران--لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | دستیاران--سقف‌سازان | کارگران عایق‌کاری، کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | نقاشان، ساختمان و نگهداری | گچ‌کاران و بناهای سیمان‌کاری | کارگران ورق‌کاری | کارگران آهن و فولاد سازه‌ای | نوارکش‌ها | کارگران و پرداخت‌کاران موزاییک درجا | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | نصّابان موکت و فرش | بنّایان سیمان‌کار و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | شیشه‌بران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | دستیاران--سقف‌سازان | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | نقاشان، ساختمان و نگهداری | گچ‌کاران و بناهای سیمان‌کاری | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | تپرز | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | تفکر انتقادی | ریاضیات | سخنرانی | گوش دادن فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | ریاضیات | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و ساخت‌وساز | ریاضیات | طراحی | زبان انگلیسی | آموزش و تربیت | مدیریت و سرپرستی | تولید و فرآوری | مهندسی و فناوری</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | ریاضیات | طراحی | زبان انگلیسی | آموزش و پرورش | مدیریت و اداره | تولید و فرآوری | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>تجسم فضایی | بینایی نزدیک | هماهنگی چندعضوی | زبردستی دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | توجه انتخابی | زبردستی انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مشکلات | بیان شفاهی | درک کتبی | درک شفاهی | قدرت بالاتنه | قدرت ایستا | دقت کنترل | وضوح گفتار | تشخیص گفتار | توجه شنیداری | درک عمق | بینایی دور | انعطاف‌پذیری حرکتی | زمان عکس‌العمل | سرعت ادراکی | تسهیلات عددی | استدلال ریاضی | استدلال استقرایی</t>
+          <t>تجسم | بینایی نزدیک | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | توجه انتخابی | مهارت انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | قدرت تنه | قدرت ایستا | دقت کنترل | وضوح گفتار | تشخیص گفتار | توجه شنیداری | درک عمق | بینایی دور | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | سرعت ادراکی | توانایی عددی | استدلال ریاضی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارگران | فشار زمانی | پیامد خطا | پیامدهای کاری و نتایج سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای خم کردن یا چرخاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | داخل ساختمان، بدون کنترل شرایط محیطی | سرعت تعیین شده توسط سرعت تجهیزات</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | فشار زمانی | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای خم کردن یا چرخاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | محیط داخلی، بدون کنترل شرایط محیطی | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | دیگ‌سازان | نجاران | نصابان دیوار خشک و تایل سقف | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | کارگران پرداخت و پولیش دستی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عایق‌کاری, کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران شابلون‌زنی، فلز و پلاستیک | مدل‌سازان، فلز و پلاستیک | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران آهن تقویتی و میلگرد | کارگران آهن و فولاد سازه‌ای | سازندگان و مونتاژکنندگان فلزات سازه‌ای | ابزارسازان و قالب‌سازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری و برنج‌کاری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نجّاران | نصابان دیوار خشک و تایل سقف | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران سنگ‌زنی و پرداخت دستی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | کارگران شابلون‌زنی، فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران آهن تقویتی و میلگرد | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0074_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0074_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | خدمات مشتریان و خدمات فردی | مکانیک | مدیریت و امور اداری | آموزش و تدریس | ریاضیات | ایمنی و امنیت عمومی | تولید و فرآوری | زبان انگلیسی | طراحی | فروش و بازاریابی | امور کارکنان و منابع انسانی | ترابری و حمل‌ونقل</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | آموزش و پرورش | ریاضیات | ایمنی و امنیت عمومی | تولید و فرآوری | زبان انگلیسی | طراحی | فروش و بازاریابی | پرسنل و منابع انسانی | حمل و نقل</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استحکام تنه | انعطاف‌پذیری کششی | حساسیت به مسئله | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | دید نزدیک | تعادل کلی بدن | استحکام ایستا | هماهنگی چنداندامی | چابکی دستی | ثبات دست و بازو | توجه انتخابی | هماهنگی کلی بدن | چابکی انگشتان | انعطاف‌پذیری طبقه‌بندی | استدلال قیاسی</t>
+          <t>قدرت تنه | انعطاف‌پذیری دامنه حرکت | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | بینایی نزدیک | تعادل کلی بدن | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | توجه انتخابی | هماهنگی کلی بدن | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | بناها و آجرچین‌ها | نصابان موکت و کف‌پوش نرم | نصابان صفحات گچی و تایل‌های سقفی | لایه‌گذاران و سازندگان قطعات فایبرگلاس | نصابان کف‌پوش، به‌جز موکت، چوب و کاشی سخت | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله و اتصالات | عایق‌کاران کف، سقف و دیوار | قالب‌گیران و ریخته‌گران، به‌جز فلز و پلاستیک | لوله‌گذاران خطوط انتقال | سفیدکاران و گچ‌کاران نما | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | اسکلت‌سازان فلزی و کارگران فولاد ساختمانی | سازندگان و نصابان سازه‌های فلزی | بتونه‌کاران و درزگیران درای‌وال | کاشی‌کاران و سنگ‌کاران | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های جوشکاری، لحیم‌کاری و بریزینگ</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | بنایان و سفت‌کاران ساختمان | موکت‌کاران و نصابان فرش | نصابان دیوار کاذب و تایل سقف | لایه‌نشانان و سازندگان فایبرگلاس | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | لوله‌گذاران خطوط انتقال | سفیدکاران و گچ‌کاران نما | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | بتونه‌کاران و درزگیران دیوار کاذب | کاشی‌کاران و سنگ‌کاران ظریف | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ساخت‌وساز و ابنیه</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | چابکی دستی | استحکام تنه | وضوح گفتار | تشخیص رنگ‌ها | تعادل کلی بدن | هماهنگی کلی بدن | انعطاف‌پذیری کششی | هماهنگی چنداندامی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | مهارت دستی | قدرت تنه | وضوح گفتار | تشخیص رنگ بصری | تعادل کلی بدن | هماهنگی کلی بدن | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بناها و آجرچین‌ها | نجاران | بتن‌ریزان و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های پوشش‌دهی، رنگ‌پاشی و اسپری | کارگران ساده ساختمانی | نصابان صفحات گچی و تایل‌های سقفی | نصابان کف‌پوش، به‌جز موکت، چوب و کاشی سخت | پرداخت‌کاران و رنگ‌کاران مصنوعات چوبی | کارگران کمکی بناها، آجرچین‌ها، سنگ‌کاران و کاشی‌کاران | کارگران کمکی نجاران | کارگران کمکی نقاشان، نصابان کاغذ دیواری و گچ‌کاران | کارگران کمکی نصابان پوشش‌های سقفی | عایق‌کاران کف، سقف و دیوار | قالب‌گیران و ریخته‌گران، به‌جز فلز و پلاستیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | موزاییک‌سازان و پرداخت‌کاران کفپوش درجا | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ساخت‌وساز و ابنیه | ریاضیات | مکانیک | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | ریاضیات | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | ثبات دست و بازو | انعطاف‌پذیری کششی | هماهنگی چنداندامی | تعادل کلی بدن | چابکی انگشتان | استحکام تنه | دقت کنترل | مرتب‌سازی اطلاعات | درک شفاهی</t>
+          <t>بینایی نزدیک | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | تعادل کلی بدن | مهارت انگشتان | قدرت تنه | دقت کنترل | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نجاران | نصابان موکت و کف‌پوش نرم | نصابان صفحات گچی و تایل‌های سقفی | لایه‌گذاران و سازندگان قطعات فایبرگلاس | نصابان کف‌پوش، به‌جز موکت، چوب و کاشی سخت | سنباده‌زنان و پرداخت‌کاران کف‌پوش چوبی | پرداخت‌کاران و رنگ‌کاران مصنوعات چوبی | شیشه‌بران و نصابان شیشه | کارگران کمکی بناها، آجرچین‌ها، سنگ‌کاران و کاشی‌کاران | کارگران کمکی نقاشان، نصابان کاغذ دیواری و گچ‌کاران | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | نقشه‌پیاده‌سازان قطعات فلزی و پلاستیکی | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | موزاییک‌سازان و پرداخت‌کاران کفپوش درجا | کاشی‌کاران و سنگ‌کاران</t>
+          <t>نجاران و درودگران | موکت‌کاران و نصابان فرش | نصابان دیوار کاذب و تایل سقف | لایه‌نشانان و سازندگان فایبرگلاس | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | شیشه‌بران و نصابان شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | ایمنی و امنیت عمومی</t>
+          <t>ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دقت کنترل | ثبات دست و بازو | درک شفاهی | استحکام ایستا | وضوح گفتار | تشخیص گفتار | ادراک عمق | دید نزدیک | حساسیت به مسئله | بیان شفاهی | انعطاف‌پذیری کششی | استقامت بدنی | استحکام تنه | زمان واکنش | کنترل نرخ حرکت | هماهنگی چنداندامی | چابکی انگشتان | چابکی دستی | توجه انتخابی | تجسم فضایی | مرتب‌سازی اطلاعات</t>
+          <t>دقت کنترل | ثبات دست و بازو | درک شفاهی | قدرت ایستا | وضوح گفتار | تشخیص گفتار | درک عمق | بینایی نزدیک | حساسیت به مسئله | بیان شفاهی | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | دیگ‌سازان صنعتی | بناها و آجرچین‌ها | نجاران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | نصابان و تعمیرکاران کنترل‌کننده‌ها و شیرآلات، به‌جز درب‌های مکانیکی | نصابان صفحات گچی و تایل‌های سقفی | نصابان و تعمیرکاران خطوط انتقال نیرو | اپراتورهای ماشین‌های حفاری و بارگیری معادن سطحی | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله و اتصالات | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | اپراتورهای ماشین‌آلات آسفالت‌کاری و تراکم | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | آرماتوربندان و نصابان میلگرد | اپراتورهای دکل حفاری دورانی نفت و گاز | سرویس‌کاران سپتیک‌تانک و لایروبان مجاری فاضلاب | کارگران ورق‌کاری فلزی | اسکلت‌سازان فلزی و کارگران فولاد ساختمانی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | نصابان دیوار کاذب و تایل سقف | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | آرماتوربندان و نصابان میلگرد | حفاران دورانی نفت و گاز | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مکانیک | طراحی | ریاضیات | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | مهندسی و فناوری | ایمنی و امنیت عمومی | فیزیک</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | طراحی | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره | مهندسی و فناوری | ایمنی و امنیت عمومی | فیزیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | چابکی انگشتان | دید نزدیک | چابکی دستی | استدلال قیاسی | استدلال استقرایی | دید دور | استحکام تنه | انعطاف‌پذیری طبقه‌بندی | تجسم فضایی | ثبات دست و بازو | درک شفاهی | بیان شفاهی | هماهنگی چنداندامی | دقت کنترل | توجه انتخابی | مرتب‌سازی اطلاعات | انعطاف‌پذیری کششی | استحکام پویا | استحکام ایستا | سرعت ادراک | انعطاف‌پذیری بستار | درک کتبی</t>
+          <t>حساسیت به مسئله | مهارت انگشتان | بینایی نزدیک | مهارت دستی | استدلال قیاسی | استدلال استقرایی | بینایی دور | قدرت تنه | انعطاف‌پذیری دسته‌بندی | تجسم | ثبات دست و بازو | درک شفاهی | بیان شفاهی | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دامنه حرکت | قدرت پویا | قدرت ایستا | سرعت ادراکی | انعطاف‌پذیری بستار | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | دیگ‌سازان صنعتی | نجاران | کارگران ساده ساختمانی | نصابان و تعمیرکاران کنترل‌کننده‌ها و شیرآلات، به‌جز درب‌های مکانیکی | برق‌کاران | مونتاژکاران موتور و ماشین‌آلات صنعتی | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع | کارگران کمکی برق‌کاران | کارگران کمکی نصابان، تعمیرکاران و تکنسین‌های خدمات | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله و اتصالات | عایق‌کاران کف، سقف و دیوار | کارگران تعمیرات و نگهداری عمومی | تعمیرکاران و نصابان ماشین‌آلات صنعتی (میلرایت) | لوله‌گذاران خطوط انتقال | سرویس‌کاران سپتیک‌تانک و لایروبان مجاری فاضلاب | کارگران ورق‌کاری فلزی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | تکنسین‌ها و اپراتورهای دیگ بخار و موتورخانه | اسکلت‌سازان فلزی و کارگران فولاد ساختمانی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | نجاران و درودگران | کارگران ساختمانی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | برق‌کاران | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌گذاران خطوط انتقال | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | کارگران ورق‌کاری فلزی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | ساخت‌وساز و ابنیه | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مهندسی و فناوری | آموزش و تدریس | طراحی | ایمنی و امنیت عمومی | رایانه و الکترونیک | تولید و فرآوری | مدیریت و امور اداری | ریاضیات</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | طراحی | ایمنی و امنیت عمومی | رایانه و الکترونیک | تولید و فرآوری | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | تشخیص گفتار | دید نزدیک | انعطاف‌پذیری کششی | حساسیت به مسئله | بیان شفاهی | درک کتبی | وضوح گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | ثبات دست و بازو | تشخیص رنگ‌ها | دید دور | چابکی انگشتان | تجسم فضایی | استحکام تنه | چابکی دستی | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی</t>
+          <t>درک شفاهی | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | حساسیت به مسئله | بیان شفاهی | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | ثبات دست و بازو | تشخیص رنگ بصری | بینایی دور | مهارت انگشتان | تجسم | قدرت تنه | مهارت دستی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه‌های زیست‌توده | نصابان و تعمیرکاران کنترل‌کننده‌ها و شیرآلات، به‌جز درب‌های مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات مرتبط | مهندسان برق | مهندسان انرژی، به‌جز باد و خورشید | تکنسین‌های انرژی زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله و اتصالات | تکنسین‌های نیروگاه‌های برق‌آبی | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | کارگران تعمیرات و نگهداری عمومی | مهندسان مکانیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | اپراتورهای نیروگاه | مدیران پروژه‌های نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | نصابان و تکنسین‌های بهینه‌سازی مصرف انرژی ساختمان | تکنسین‌های تعمیر و نگهداری توربین بادی</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | تکنسین‌های سامانه‌های زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | تکنسین‌های نیروگاه برقابی | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | کارگران عمومی تعمیرات و نگهداری تاسیسات | مهندسان مکانیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | اپراتورهای نیروگاه برق | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | نصابان و تکنسین‌های عایق‌کاری و بهسازی مصرف انرژی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مدیریت و امور اداری | طراحی | زبان انگلیسی | خدمات مشتریان و خدمات فردی</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | طراحی | زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | چابکی دستی | انعطاف‌پذیری کششی | استحکام تنه | هماهنگی چنداندامی | استحکام ایستا | تعادل کلی بدن | بیان شفاهی | حساسیت به مسئله | استقامت بدنی | استحکام پویا | تجسم فضایی | وضوح گفتار | تشخیص رنگ‌ها | هماهنگی کلی بدن | دقت کنترل | چابکی انگشتان | مرتب‌سازی اطلاعات | درک شفاهی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو | قدرت ایستا | تعادل کلی بدن | بیان شفاهی | حساسیت به مسئله | استقامت | قدرت پویا | تجسم | وضوح گفتار | تشخیص رنگ بصری | هماهنگی کلی بدن | دقت کنترل | مهارت انگشتان | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بناها و آجرچین‌ها | نجاران | بتن‌ریزان و پرداخت‌کاران بتن | نصابان صفحات گچی و تایل‌های سقفی | نصابان کف‌پوش، به‌جز موکت، چوب و کاشی سخت | پرداخت‌کاران و رنگ‌کاران مصنوعات چوبی | شیشه‌بران و نصابان شیشه | کارگران کمکی بناها، آجرچین‌ها، سنگ‌کاران و کاشی‌کاران | کارگران کمکی نجاران | کارگران کمکی نقاشان، نصابان کاغذ دیواری و گچ‌کاران | کارگران کمکی نصابان پوشش‌های سقفی | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | قالب‌گیران و ریخته‌گران، به‌جز فلز و پلاستیک | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | عایق‌کاران و نصابان پوشش‌های سقفی | بتونه‌کاران و درزگیران درای‌وال | موزاییک‌سازان و پرداخت‌کاران کفپوش درجا | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | شیشه‌بران و نصابان شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | عایق‌کاران و نصابان پوشش‌های سقفی | بتونه‌کاران و درزگیران دیوار کاذب | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | ریاضیات | مدیریت و امور اداری | طراحی | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | مدیریت و اداره | طراحی | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استحکام تنه | استحکام ایستا | هماهنگی چنداندامی | چابکی دستی | انعطاف‌پذیری کششی | ثبات دست و بازو | استقامت بدنی | دید نزدیک | چابکی انگشتان | دقت کنترل | زمان واکنش | حساسیت به مسئله | استحکام پویا | تعادل کلی بدن | هماهنگی کلی بدن | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>قدرت تنه | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | استقامت | بینایی نزدیک | مهارت انگشتان | دقت کنترل | زمان عکس‌العمل | حساسیت به مسئله | قدرت پویا | تعادل کلی بدن | هماهنگی کلی بدن | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | دیگ‌سازان صنعتی | بناها و آجرچین‌ها | نجاران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | نصابان صفحات گچی و تایل‌های سقفی | نصابان حصار و فنس | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | کارگران کمکی بناها، آجرچین‌ها، سنگ‌کاران و کاشی‌کاران | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | نقشه‌پیاده‌سازان قطعات فلزی و پلاستیکی | تعمیرکاران و نصابان ماشین‌آلات صنعتی (میلرایت) | لوله‌گذاران خطوط انتقال | کارگران ورق‌کاری فلزی | اسکلت‌سازان فلزی و کارگران فولاد ساختمانی | سازندگان و نصابان سازه‌های فلزی | موزاییک‌سازان و پرداخت‌کاران کفپوش درجا | تنظیم‌کنندگان و اپراتورهای ماشین‌های صنایع چوب، به‌جز اره‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | نصابان فنس و حصار | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌گذاران خطوط انتقال | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | آموزش و تدریس | ریاضیات | طراحی | مکانیک | مدیریت و امور اداری</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | آموزش و پرورش | ریاضیات | طراحی | مکانیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تعادل کلی بدن | انعطاف‌پذیری کششی | استحکام تنه | حساسیت به مسئله | دید نزدیک | هماهنگی چنداندامی | چابکی دستی | ثبات دست و بازو | درک شفاهی | هماهنگی کلی بدن | استقامت بدنی | استحکام ایستا | دقت کنترل | چابکی انگشتان | دید دور | تشخیص گفتار | توجه انتخابی | تجسم فضایی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
+          <t>تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | حساسیت به مسئله | بینایی نزدیک | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | درک شفاهی | هماهنگی کلی بدن | استقامت | قدرت ایستا | دقت کنترل | مهارت انگشتان | بینایی دور | تشخیص گفتار | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بناها و آجرچین‌ها | نجاران | نصابان موکت و کف‌پوش نرم | بتن‌ریزان و پرداخت‌کاران بتن | نصابان صفحات گچی و تایل‌های سقفی | نصابان کف‌پوش، به‌جز موکت، چوب و کاشی سخت | شیشه‌بران و نصابان شیشه | کارگران کمکی بناها، آجرچین‌ها، سنگ‌کاران و کاشی‌کاران | کارگران کمکی نقاشان، نصابان کاغذ دیواری و گچ‌کاران | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله و اتصالات | کارگران کمکی نصابان پوشش‌های سقفی | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | نقاشان ساختمان و تاسیسات | سفیدکاران و گچ‌کاران نما | کارگران ورق‌کاری فلزی | اسکلت‌سازان فلزی و کارگران فولاد ساختمانی | بتونه‌کاران و درزگیران درای‌وال | موزاییک‌سازان و پرداخت‌کاران کفپوش درجا | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | شیشه‌بران و نصابان شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | نقاشان ساختمان و تاسیسات | سفیدکاران و گچ‌کاران نما | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | بتونه‌کاران و درزگیران دیوار کاذب | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | تفکر انتقادی | ریاضیات | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | ریاضیات | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | ساخت‌وساز و ابنیه | ریاضیات | طراحی | زبان انگلیسی | آموزش و تدریس | مدیریت و امور اداری | تولید و فرآوری | مهندسی و فناوری</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | ریاضیات | طراحی | زبان انگلیسی | آموزش و پرورش | مدیریت و اداره | تولید و فرآوری | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | هماهنگی چنداندامی | چابکی دستی | ثبات دست و بازو | مرتب‌سازی اطلاعات | توجه انتخابی | چابکی انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری طبقه‌بندی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | استحکام تنه | استحکام ایستا | دقت کنترل | وضوح گفتار | تشخیص گفتار | توجه شنیداری | ادراک عمق | دید دور | انعطاف‌پذیری کششی | زمان واکنش | سرعت ادراک | سهولت استفاده از اعداد | استدلال ریاضی | استدلال استقرایی</t>
+          <t>تجسم | بینایی نزدیک | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | توجه انتخابی | مهارت انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | قدرت تنه | قدرت ایستا | دقت کنترل | وضوح گفتار | تشخیص گفتار | توجه شنیداری | درک عمق | بینایی دور | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | سرعت ادراکی | توانایی عددی | استدلال ریاضی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | دیگ‌سازان صنعتی | نجاران | نصابان صفحات گچی و تایل‌های سقفی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و ماشین‌آلات صنعتی | پرداخت‌کاران و سنگ‌زن‌های دستی قطعات | مکانیک‌های ماشین‌آلات صنعتی | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | نقشه‌پیاده‌سازان قطعات فلزی و پلاستیکی | ماکت‌سازان و مدل‌سازان قطعات فلزی و پلاستیکی | قالب‌گیران و ریخته‌گران، به‌جز فلز و پلاستیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | آرماتوربندان و نصابان میلگرد | اسکلت‌سازان فلزی و کارگران فولاد ساختمانی | سازندگان و نصابان سازه‌های فلزی | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های جوشکاری، لحیم‌کاری و بریزینگ | تنظیم‌کنندگان و اپراتورهای ماشین‌های صنایع چوب، به‌جز اره‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | نجاران و درودگران | نصابان دیوار کاذب و تایل سقف | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | مکانیک‌های ماشین‌آلات صنعتی | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | مدل‌سازان فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | آرماتوربندان و نصابان میلگرد | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
